--- a/torivac-web/dist/assets/data/prices.demo.xlsx
+++ b/torivac-web/dist/assets/data/prices.demo.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-10-27T23:10:59Z</t>
+          <t>2026-10-27T23:14:07Z</t>
         </is>
       </c>
     </row>

--- a/torivac-web/dist/assets/data/prices.demo.xlsx
+++ b/torivac-web/dist/assets/data/prices.demo.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-10-27T23:14:07Z</t>
+          <t>2026-10-27T23:22:14Z</t>
         </is>
       </c>
     </row>

--- a/torivac-web/dist/assets/data/prices.demo.xlsx
+++ b/torivac-web/dist/assets/data/prices.demo.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-10-27T23:22:14Z</t>
+          <t>2026-10-28T07:01:05Z</t>
         </is>
       </c>
     </row>

--- a/torivac-web/dist/assets/data/prices.demo.xlsx
+++ b/torivac-web/dist/assets/data/prices.demo.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-10-28T07:01:05Z</t>
+          <t>2026-10-28T07:23:34Z</t>
         </is>
       </c>
     </row>

--- a/torivac-web/dist/assets/data/prices.demo.xlsx
+++ b/torivac-web/dist/assets/data/prices.demo.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-10-28T07:23:34Z</t>
+          <t>2026-10-28T07:27:50Z</t>
         </is>
       </c>
     </row>

--- a/torivac-web/dist/assets/data/prices.demo.xlsx
+++ b/torivac-web/dist/assets/data/prices.demo.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -5022,7 +5022,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -5081,7 +5081,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>2026-10-28T07:27:50Z</t>
+          <t>2026-10-28T07:38:15Z</t>
         </is>
       </c>
     </row>
